--- a/data/trans_dic/KIDM_C_2_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_2_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor)</t>
+          <t>Menores con mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,85</t>
+          <t>0,0; 17,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,0; 7,41</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,1</t>
+          <t>1,12; 10,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,85</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,02</t>
+          <t>1,38; 6,11</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 12,37</t>
+          <t>1,28; 11,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,75</t>
+          <t>0,75; 7,29</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,86</t>
+          <t>1,0; 4,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,85</t>
+          <t>1,05; 4,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,93</t>
+          <t>1,38; 3,99</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con mucho o muchísimo cansancio para disfrutar de las cosas que le gustan (autopercepción menor) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5356</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5871</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>602; 5511</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2164; 9564</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4627</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>829; 7552</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1033; 10006</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1498</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1498</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5483</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5367</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5149</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6572</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11722</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2097; 10461</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2850; 12076</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6680; 19244</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_C_2_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_2_R-Habitat-trans_dic.xlsx
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,18</t>
+          <t>0,0; 19,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 8,49</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,27</t>
+          <t>1,08; 10,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,59</t>
+          <t>0,58; 5,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,11</t>
+          <t>1,22; 5,84</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,62</t>
+          <t>1,28; 12,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,29</t>
+          <t>0,9; 7,59</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,73</t>
+          <t>0,0; 8,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,97</t>
+          <t>0,97; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,44</t>
+          <t>1,03; 4,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,99</t>
+          <t>1,38; 3,92</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5356</t>
+          <t>0; 6061</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5871</t>
+          <t>0; 6720</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>602; 5511</t>
+          <t>582; 5693</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5746</t>
+          <t>591; 6062</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2164; 9564</t>
+          <t>1912; 9135</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4627</t>
+          <t>0; 4487</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>829; 7552</t>
+          <t>833; 8240</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1033; 10006</t>
+          <t>1233; 10405</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5483</t>
+          <t>0; 4639</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5367</t>
+          <t>0; 5240</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2097; 10461</t>
+          <t>2036; 10493</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2850; 12076</t>
+          <t>2791; 12392</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6680; 19244</t>
+          <t>6662; 18912</t>
         </is>
       </c>
     </row>
